--- a/output/pdf_financials_xlsx/RJX.A.xlsx
+++ b/output/pdf_financials_xlsx/RJX.A.xlsx
@@ -7366,16 +7366,16 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.669463</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.497698</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.629122</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>0</v>
@@ -22749,7 +22749,11 @@
           <t>Non-cash exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -23941,7 +23945,11 @@
           <t>Exploration and evaluation expenditures (Note 5)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RJX.A.xlsx
+++ b/output/pdf_financials_xlsx/RJX.A.xlsx
@@ -1033,19 +1033,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.015534</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000152</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000691</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1060,28 +1060,28 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000308</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.002501</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.003397</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000104</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.011239</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.026328</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.007885</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.001442</v>
       </c>
     </row>
     <row r="13">
@@ -1999,19 +1999,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.850394</v>
+        <v>-0.865928</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.54612</v>
+        <v>-0.546272</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.55302</v>
+        <v>-1.55332</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.024056</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.503165</v>
+        <v>-0.503856</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.316177</v>
@@ -2026,28 +2026,28 @@
         <v>0.05335</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.83331</v>
+        <v>-3.833618</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.920076</v>
+        <v>-0.922577</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.678389</v>
+        <v>-2.681786</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.106284</v>
+        <v>-2.106388</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.680519</v>
+        <v>-0.691758</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.633057</v>
+        <v>-0.659385</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.523264</v>
+        <v>-0.531149</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.130294</v>
+        <v>-0.131736</v>
       </c>
     </row>
     <row r="28">
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.850394</v>
+        <v>-0.865928</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.54612</v>
+        <v>-0.546272</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.550808</v>
+        <v>-1.551108</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.021843</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.497938</v>
+        <v>-0.498629</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.31095</v>
@@ -2142,28 +2142,28 @@
         <v>0.061294</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.825366</v>
+        <v>-3.825674</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.912945</v>
+        <v>-0.915446</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.662482</v>
+        <v>-2.665879</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.106284</v>
+        <v>-2.106388</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.680519</v>
+        <v>-0.691758</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.633057</v>
+        <v>-0.659385</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.523264</v>
+        <v>-0.531149</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.130294</v>
+        <v>-0.131736</v>
       </c>
     </row>
     <row r="30">
@@ -2422,55 +2422,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.266809</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.153989</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.153989</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.608044</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.354247</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.045953</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.010285</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.012932</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.12932</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.535684</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.698723</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.820966</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.280632</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.962477</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.380911</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.21078</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.02235</v>
       </c>
     </row>
     <row r="35">
@@ -2538,55 +2538,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.266809</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.153989</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.153989</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.608044</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.354247</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.045953</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.010285</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.012932</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.12932</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.535684</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.698723</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.820966</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.280632</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.962477</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.380911</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.21078</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.02235</v>
       </c>
     </row>
     <row r="37">
@@ -3234,55 +3234,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.269815</v>
+        <v>0.003006</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.156074</v>
+        <v>0.002085</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.153989</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.61117</v>
+        <v>0.003126</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.358511</v>
+        <v>0.004264</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.046191</v>
+        <v>0.000238</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.010513</v>
+        <v>0.000228</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.013156</v>
+        <v>0.000224</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.129526</v>
+        <v>0.000206</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.5358849999999999</v>
+        <v>0.000201</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.698918</v>
+        <v>0.000195</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.821179</v>
+        <v>0.000213</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.280632</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.962477</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.380911</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.21078</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.02421</v>
+        <v>0.00186</v>
       </c>
     </row>
     <row r="49">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -17021,7 +17021,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -35950,7 +35950,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E279" s="5" t="n">

--- a/output/pdf_financials_xlsx/RJX.A.xlsx
+++ b/output/pdf_financials_xlsx/RJX.A.xlsx
@@ -2093,19 +2093,19 @@
         <v>0.015907</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.005803</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.006094</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.006675</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.006675</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.006675</v>
       </c>
     </row>
     <row r="29">
@@ -2151,19 +2151,19 @@
         <v>-2.665879</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.106388</v>
+        <v>-2.100585</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.691758</v>
+        <v>-0.6856640000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.659385</v>
+        <v>-0.65271</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.531149</v>
+        <v>-0.524474</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.131736</v>
+        <v>-0.125061</v>
       </c>
     </row>
     <row r="30">
@@ -6331,19 +6331,19 @@
         <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.005803</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.006094</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.006675</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.006675</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.006675</v>
       </c>
     </row>
     <row r="101">
@@ -20146,7 +20146,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RJX.A.xlsx
+++ b/output/pdf_financials_xlsx/RJX.A.xlsx
@@ -4387,46 +4387,46 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0229</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.023597</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.024095</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0173</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0173</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.011375</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.011375</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.015875</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.040772</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.1253</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="68">
@@ -4585,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.010346</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>0</v>
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.010346</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>0</v>
@@ -4875,7 +4875,7 @@
         <v>0.170828</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.181174</v>
+        <v>0.170828</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>0.170828</v>
@@ -5186,10 +5186,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.006587530554718973</v>
       </c>
       <c r="N80" s="1" t="inlineStr">
         <is>
@@ -6353,10 +6351,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.007577</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.025242</v>
@@ -6643,10 +6641,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.125438</v>
+        <v>-0.117861</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.02646</v>
+        <v>-0.025539</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.054272</v>
@@ -6972,7 +6970,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008715000000000001</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -8344,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008715000000000001</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -8402,7 +8400,7 @@
         <v>-1.591308</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-0.761684</v>
+        <v>-0.7703989999999999</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-0.581566</v>
@@ -12856,7 +12854,11 @@
           <t>Lease obligations (Note 8)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -20926,7 +20928,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -21844,7 +21850,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -22036,7 +22046,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -24854,7 +24868,11 @@
           <t>Funds to be received from private placement $</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -26931,7 +26949,11 @@
           <t>NET INCOME (LOSS) $</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -28153,7 +28175,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -28355,7 +28381,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -29876,7 +29906,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E217" s="5" t="n">
         <v>0.007577</v>
       </c>
@@ -37150,7 +37184,11 @@
           <t>Future income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
